--- a/Dữ liệu Kho.xlsx
+++ b/Dữ liệu Kho.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HK2Nam2\PTTKHTTT\DoAn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E8944A-BB51-4178-B3CA-A416F8968B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A364D58B-EB37-4090-B052-EB6E69454099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,6 +370,13 @@
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -475,5 +482,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>